--- a/nr-update-system-nss/ig/ValueSet-fr-core-vs-contact-relationship.xlsx
+++ b/nr-update-system-nss/ig/ValueSet-fr-core-vs-contact-relationship.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-22T17:34:51+00:00</t>
+    <t>2026-02-23T07:43:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-system-nss/ig/ValueSet-fr-core-vs-contact-relationship.xlsx
+++ b/nr-update-system-nss/ig/ValueSet-fr-core-vs-contact-relationship.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot-2</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:28:50+00:00</t>
+    <t>2026-03-25T14:42:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
